--- a/詳細設計/DB詳細設計/01_DB-DD-01_ユーザー・組織・権限DB詳細設計書.xlsx
+++ b/詳細設計/DB詳細設計/01_DB-DD-01_ユーザー・組織・権限DB詳細設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R9f0d7c0254a04fd7"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R565f9d5423fd43b8"/>
-    <ns0:sheet name="02_Table一覧・作成順" sheetId="3" ns1:id="Rfbdedd1edbc54bb5"/>
-    <ns0:sheet name="03_ER・制約一覧" sheetId="4" ns1:id="R1df61bd719ba45ee"/>
-    <ns0:sheet name="04_Table詳細・DDL" sheetId="5" ns1:id="Raa0410c4879c4a13"/>
-    <ns0:sheet name="99_Status・初期Data" sheetId="6" ns1:id="R3cac3e7169994ab1"/>
-    <ns0:sheet name="05_単体テスト観点" sheetId="7" ns1:id="R40b66ba9fdf04c9c"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9579ff82e6f14407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R6494ac6a405b4d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧・作成順" sheetId="3" r:id="Rb749d2871dcc4e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ER・制約一覧" sheetId="4" r:id="R4aacafef5a6641c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Table詳細・DDL" sheetId="5" r:id="R3ca64538834041f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Status・初期Data" sheetId="6" r:id="R564a3f2806004482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_単体テスト観点" sheetId="7" r:id="R43ff0bff1f6240be"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="00000"/>
+    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -123,7 +124,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -183,6 +184,10 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -439,7 +444,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -583,7 +588,7 @@
       <x:c r="E12" s="14"/>
       <x:c r="F12" s="14"/>
       <x:c r="G12" s="14" t="str">
-        <x:v>Review中</x:v>
+        <x:v>Review済／承認待ち</x:v>
       </x:c>
       <x:c r="H12" s="14"/>
       <x:c r="I12" s="14"/>
@@ -639,7 +644,7 @@
       <x:c r="K15" s="15"/>
       <x:c r="L15" s="15"/>
     </x:row>
-    <x:row r="16" ht="34" customHeight="1">
+    <x:row r="16" ht="60" customHeight="1">
       <x:c r="A16" s="14" t="str">
         <x:v>参照Baseline</x:v>
       </x:c>
@@ -649,7 +654,8 @@
       <x:c r="E16" s="14"/>
       <x:c r="F16" s="14"/>
       <x:c r="G16" s="14" t="str">
-        <x:v>BL-2026-09-24＋各参照文書の最新改訂</x:v>
+        <x:v>BL-2026-09-24＋CHG-DB-20260929-01
+作成・Review根拠：15／02／16／17／19 各Ver.2.6（02参照資料欄）。</x:v>
       </x:c>
       <x:c r="H16" s="14"/>
       <x:c r="I16" s="14"/>
@@ -693,9 +699,9 @@
       <x:c r="K18" s="14"/>
       <x:c r="L18" s="14"/>
     </x:row>
-    <x:row r="19" ht="29" customHeight="1">
+    <x:row r="19" ht="36" customHeight="1">
       <x:c r="A19" s="17" t="str">
-        <x:v>責任者欄は署名時に記入。文書状態は承認操作までReview中。</x:v>
+        <x:v>二次Review：2026-09-30。責任者欄は署名時に記入。正式承認まで承認待ちとする。</x:v>
       </x:c>
       <x:c r="B19" s="17"/>
       <x:c r="C19" s="17"/>
@@ -714,7 +720,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="G7:L7"/>
@@ -727,7 +732,6 @@
     <x:mergeCell ref="A11:F11"/>
     <x:mergeCell ref="G11:L11"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="G12:L12"/>
     <x:mergeCell ref="A13:F13"/>
     <x:mergeCell ref="G13:L13"/>
     <x:mergeCell ref="A14:F14"/>
@@ -735,12 +739,14 @@
     <x:mergeCell ref="A15:F15"/>
     <x:mergeCell ref="G15:L15"/>
     <x:mergeCell ref="A16:F16"/>
-    <x:mergeCell ref="G16:L16"/>
     <x:mergeCell ref="A17:F17"/>
     <x:mergeCell ref="G17:L17"/>
     <x:mergeCell ref="A18:F18"/>
     <x:mergeCell ref="G18:L18"/>
+    <x:mergeCell ref="G12:L12"/>
     <x:mergeCell ref="A19:L19"/>
+    <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="G16:L16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -803,7 +809,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -949,12 +955,41 @@
       </x:c>
       <x:c r="L10" s="23"/>
     </x:row>
+    <x:row r="11" ht="110" customHeight="1">
+      <x:c r="A11" s="20" t="str">
+        <x:v>Ver.2.1</x:v>
+      </x:c>
+      <x:c r="B11" s="27" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C11" s="20"/>
+      <x:c r="D11" s="20" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="E11" s="20" t="str">
+        <x:v>二次Review完了。BL-2026-09-24＋CHG-DB-20260929-01、作成時参照版15/02/16/17/19 Ver.2.6へ固定。DB設計変更なし。</x:v>
+      </x:c>
+      <x:c r="F11" s="20"/>
+      <x:c r="G11" s="20" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H11" s="20" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="I11" s="20"/>
+      <x:c r="J11" s="20" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
+      <x:c r="L11" s="20"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="B7:C7"/>
     <x:mergeCell ref="E7:F7"/>
@@ -972,6 +1007,11 @@
     <x:mergeCell ref="E10:F10"/>
     <x:mergeCell ref="H10:I10"/>
     <x:mergeCell ref="K10:L10"/>
+    <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="B11:C11"/>
+    <x:mergeCell ref="E11:F11"/>
+    <x:mergeCell ref="H11:I11"/>
+    <x:mergeCell ref="K11:L11"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1034,7 +1074,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -2227,7 +2267,7 @@
       <x:c r="K47" s="11"/>
       <x:c r="L47" s="11"/>
     </x:row>
-    <x:row r="48" ht="34" customHeight="1">
+    <x:row r="48" ht="50" customHeight="1">
       <x:c r="A48" s="14" t="str">
         <x:v>15_DB基本設計書</x:v>
       </x:c>
@@ -2235,7 +2275,7 @@
       <x:c r="C48" s="14"/>
       <x:c r="D48" s="14"/>
       <x:c r="E48" s="14" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>Ver.2.6（作成時参照版）</x:v>
       </x:c>
       <x:c r="F48" s="14"/>
       <x:c r="G48" s="14"/>
@@ -2374,7 +2414,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A16:L16"/>
     <x:mergeCell ref="A29:L29"/>
@@ -2428,7 +2467,6 @@
     <x:mergeCell ref="E47:H47"/>
     <x:mergeCell ref="I47:L47"/>
     <x:mergeCell ref="A48:D48"/>
-    <x:mergeCell ref="E48:H48"/>
     <x:mergeCell ref="I48:L48"/>
     <x:mergeCell ref="A49:D49"/>
     <x:mergeCell ref="E49:H49"/>
@@ -2448,6 +2486,8 @@
     <x:mergeCell ref="A54:D54"/>
     <x:mergeCell ref="E54:H54"/>
     <x:mergeCell ref="I54:L54"/>
+    <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="E48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2510,7 +2550,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -5251,10 +5291,10 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A18:L18"/>
     <x:mergeCell ref="A59:L59"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5317,7 +5357,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -11438,7 +11478,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A5:L5"/>
     <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="A8:D8"/>
@@ -11723,6 +11762,7 @@
     <x:mergeCell ref="I297:L297"/>
     <x:mergeCell ref="A268:L268"/>
     <x:mergeCell ref="A298:L298"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -11785,7 +11825,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -15080,7 +15120,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:B7"/>
     <x:mergeCell ref="C7:D7"/>
@@ -15550,6 +15589,7 @@
     <x:mergeCell ref="D177:F177"/>
     <x:mergeCell ref="G177:I177"/>
     <x:mergeCell ref="J177:L177"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -15612,7 +15652,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -22328,7 +22368,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="A8:L8"/>
@@ -22369,6 +22408,7 @@
     <x:mergeCell ref="E197:H197"/>
     <x:mergeCell ref="I197:L197"/>
     <x:mergeCell ref="A198:L198"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/詳細設計/DB詳細設計/01_DB-DD-01_ユーザー・組織・権限DB詳細設計書.xlsx
+++ b/詳細設計/DB詳細設計/01_DB-DD-01_ユーザー・組織・権限DB詳細設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9579ff82e6f14407"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R6494ac6a405b4d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧・作成順" sheetId="3" r:id="Rb749d2871dcc4e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ER・制約一覧" sheetId="4" r:id="R4aacafef5a6641c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Table詳細・DDL" sheetId="5" r:id="R3ca64538834041f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Status・初期Data" sheetId="6" r:id="R564a3f2806004482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_単体テスト観点" sheetId="7" r:id="R43ff0bff1f6240be"/>
-  </x:sheets>
-</x:workbook>
+<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheets>
+    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="R9f0d7c0254a04fd7"/>
+    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R565f9d5423fd43b8"/>
+    <ns0:sheet name="02_Table一覧・作成順" sheetId="3" ns1:id="Rfbdedd1edbc54bb5"/>
+    <ns0:sheet name="03_ER・制約一覧" sheetId="4" ns1:id="R1df61bd719ba45ee"/>
+    <ns0:sheet name="04_Table詳細・DDL" sheetId="5" ns1:id="Raa0410c4879c4a13"/>
+    <ns0:sheet name="99_Status・初期Data" sheetId="6" ns1:id="R3cac3e7169994ab1"/>
+    <ns0:sheet name="05_単体テスト観点" sheetId="7" ns1:id="R40b66ba9fdf04c9c"/>
+  </ns0:sheets>
+</ns0:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,9 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="00000"/>
-    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -124,7 +123,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -184,10 +183,6 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -444,7 +439,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -588,7 +583,7 @@
       <x:c r="E12" s="14"/>
       <x:c r="F12" s="14"/>
       <x:c r="G12" s="14" t="str">
-        <x:v>Review済／承認待ち</x:v>
+        <x:v>Review中</x:v>
       </x:c>
       <x:c r="H12" s="14"/>
       <x:c r="I12" s="14"/>
@@ -644,7 +639,7 @@
       <x:c r="K15" s="15"/>
       <x:c r="L15" s="15"/>
     </x:row>
-    <x:row r="16" ht="60" customHeight="1">
+    <x:row r="16" ht="34" customHeight="1">
       <x:c r="A16" s="14" t="str">
         <x:v>参照Baseline</x:v>
       </x:c>
@@ -654,8 +649,7 @@
       <x:c r="E16" s="14"/>
       <x:c r="F16" s="14"/>
       <x:c r="G16" s="14" t="str">
-        <x:v>BL-2026-09-24＋CHG-DB-20260929-01
-作成・Review根拠：15／02／16／17／19 各Ver.2.6（02参照資料欄）。</x:v>
+        <x:v>BL-2026-09-24＋各参照文書の最新改訂</x:v>
       </x:c>
       <x:c r="H16" s="14"/>
       <x:c r="I16" s="14"/>
@@ -699,9 +693,9 @@
       <x:c r="K18" s="14"/>
       <x:c r="L18" s="14"/>
     </x:row>
-    <x:row r="19" ht="36" customHeight="1">
+    <x:row r="19" ht="29" customHeight="1">
       <x:c r="A19" s="17" t="str">
-        <x:v>二次Review：2026-09-30。責任者欄は署名時に記入。正式承認まで承認待ちとする。</x:v>
+        <x:v>責任者欄は署名時に記入。文書状態は承認操作までReview中。</x:v>
       </x:c>
       <x:c r="B19" s="17"/>
       <x:c r="C19" s="17"/>
@@ -720,6 +714,7 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="G7:L7"/>
@@ -732,6 +727,7 @@
     <x:mergeCell ref="A11:F11"/>
     <x:mergeCell ref="G11:L11"/>
     <x:mergeCell ref="A12:F12"/>
+    <x:mergeCell ref="G12:L12"/>
     <x:mergeCell ref="A13:F13"/>
     <x:mergeCell ref="G13:L13"/>
     <x:mergeCell ref="A14:F14"/>
@@ -739,14 +735,12 @@
     <x:mergeCell ref="A15:F15"/>
     <x:mergeCell ref="G15:L15"/>
     <x:mergeCell ref="A16:F16"/>
+    <x:mergeCell ref="G16:L16"/>
     <x:mergeCell ref="A17:F17"/>
     <x:mergeCell ref="G17:L17"/>
     <x:mergeCell ref="A18:F18"/>
     <x:mergeCell ref="G18:L18"/>
-    <x:mergeCell ref="G12:L12"/>
     <x:mergeCell ref="A19:L19"/>
-    <x:mergeCell ref="A3:L3"/>
-    <x:mergeCell ref="G16:L16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -809,7 +803,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -955,41 +949,12 @@
       </x:c>
       <x:c r="L10" s="23"/>
     </x:row>
-    <x:row r="11" ht="110" customHeight="1">
-      <x:c r="A11" s="20" t="str">
-        <x:v>Ver.2.1</x:v>
-      </x:c>
-      <x:c r="B11" s="27" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="C11" s="20"/>
-      <x:c r="D11" s="20" t="str">
-        <x:v>Review</x:v>
-      </x:c>
-      <x:c r="E11" s="20" t="str">
-        <x:v>二次Review完了。BL-2026-09-24＋CHG-DB-20260929-01、作成時参照版15/02/16/17/19 Ver.2.6へ固定。DB設計変更なし。</x:v>
-      </x:c>
-      <x:c r="F11" s="20"/>
-      <x:c r="G11" s="20" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="H11" s="20" t="str">
-        <x:v>Review済</x:v>
-      </x:c>
-      <x:c r="I11" s="20"/>
-      <x:c r="J11" s="20" t="str">
-        <x:v>－</x:v>
-      </x:c>
-      <x:c r="K11" s="20" t="str">
-        <x:v>承認待ち</x:v>
-      </x:c>
-      <x:c r="L11" s="20"/>
-    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="B7:C7"/>
     <x:mergeCell ref="E7:F7"/>
@@ -1007,11 +972,6 @@
     <x:mergeCell ref="E10:F10"/>
     <x:mergeCell ref="H10:I10"/>
     <x:mergeCell ref="K10:L10"/>
-    <x:mergeCell ref="A3:L3"/>
-    <x:mergeCell ref="B11:C11"/>
-    <x:mergeCell ref="E11:F11"/>
-    <x:mergeCell ref="H11:I11"/>
-    <x:mergeCell ref="K11:L11"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1074,7 +1034,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -2267,7 +2227,7 @@
       <x:c r="K47" s="11"/>
       <x:c r="L47" s="11"/>
     </x:row>
-    <x:row r="48" ht="50" customHeight="1">
+    <x:row r="48" ht="34" customHeight="1">
       <x:c r="A48" s="14" t="str">
         <x:v>15_DB基本設計書</x:v>
       </x:c>
@@ -2275,7 +2235,7 @@
       <x:c r="C48" s="14"/>
       <x:c r="D48" s="14"/>
       <x:c r="E48" s="14" t="str">
-        <x:v>Ver.2.6（作成時参照版）</x:v>
+        <x:v>Ver.2.6</x:v>
       </x:c>
       <x:c r="F48" s="14"/>
       <x:c r="G48" s="14"/>
@@ -2414,6 +2374,7 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A16:L16"/>
     <x:mergeCell ref="A29:L29"/>
@@ -2467,6 +2428,7 @@
     <x:mergeCell ref="E47:H47"/>
     <x:mergeCell ref="I47:L47"/>
     <x:mergeCell ref="A48:D48"/>
+    <x:mergeCell ref="E48:H48"/>
     <x:mergeCell ref="I48:L48"/>
     <x:mergeCell ref="A49:D49"/>
     <x:mergeCell ref="E49:H49"/>
@@ -2486,8 +2448,6 @@
     <x:mergeCell ref="A54:D54"/>
     <x:mergeCell ref="E54:H54"/>
     <x:mergeCell ref="I54:L54"/>
-    <x:mergeCell ref="A3:L3"/>
-    <x:mergeCell ref="E48:H48"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2550,7 +2510,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -5291,10 +5251,10 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A18:L18"/>
     <x:mergeCell ref="A59:L59"/>
-    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5357,7 +5317,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -11478,6 +11438,7 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A5:L5"/>
     <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="A8:D8"/>
@@ -11762,7 +11723,6 @@
     <x:mergeCell ref="I297:L297"/>
     <x:mergeCell ref="A268:L268"/>
     <x:mergeCell ref="A298:L298"/>
-    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -11825,7 +11785,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -15120,6 +15080,7 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:B7"/>
     <x:mergeCell ref="C7:D7"/>
@@ -15589,7 +15550,6 @@
     <x:mergeCell ref="D177:F177"/>
     <x:mergeCell ref="G177:I177"/>
     <x:mergeCell ref="J177:L177"/>
-    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -15652,7 +15612,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -22368,6 +22328,7 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="A8:L8"/>
@@ -22408,7 +22369,6 @@
     <x:mergeCell ref="E197:H197"/>
     <x:mergeCell ref="I197:L197"/>
     <x:mergeCell ref="A198:L198"/>
-    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/詳細設計/DB詳細設計/01_DB-DD-01_ユーザー・組織・権限DB詳細設計書.xlsx
+++ b/詳細設計/DB詳細設計/01_DB-DD-01_ユーザー・組織・権限DB詳細設計書.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R9579ff82e6f14407"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R6494ac6a405b4d86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧・作成順" sheetId="3" r:id="Rb749d2871dcc4e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ER・制約一覧" sheetId="4" r:id="R4aacafef5a6641c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Table詳細・DDL" sheetId="5" r:id="R3ca64538834041f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Status・初期Data" sheetId="6" r:id="R564a3f2806004482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_単体テスト観点" sheetId="7" r:id="R43ff0bff1f6240be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R0fc70856c2c24e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R594af1f8e11849f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧・作成順" sheetId="3" r:id="R5740e009e56747d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ER・制約一覧" sheetId="4" r:id="Rd9b5deb0f7bc462c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Table詳細・DDL" sheetId="5" r:id="Rb3ee8d4752a44c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Status・初期Data" sheetId="6" r:id="Rf7d5ae64a6344d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_単体テスト観点" sheetId="7" r:id="Rdd092c32c0da4c45"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3326,7 +3326,7 @@
         <x:v>23505</x:v>
       </x:c>
       <x:c r="K27" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A8:H8</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A8:H8</x:v>
       </x:c>
       <x:c r="L27" s="15" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -3364,7 +3364,7 @@
         <x:v>23505</x:v>
       </x:c>
       <x:c r="K28" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A9:H9</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A9:H9</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -3402,7 +3402,7 @@
         <x:v>23505</x:v>
       </x:c>
       <x:c r="K29" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A10:H10</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A10:H10</x:v>
       </x:c>
       <x:c r="L29" s="15" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -3440,7 +3440,7 @@
         <x:v>23505</x:v>
       </x:c>
       <x:c r="K30" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A11:H11</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A11:H11</x:v>
       </x:c>
       <x:c r="L30" s="14" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -3478,7 +3478,7 @@
         <x:v>23505</x:v>
       </x:c>
       <x:c r="K31" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A12:H12</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A12:H12</x:v>
       </x:c>
       <x:c r="L31" s="15" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -3516,7 +3516,7 @@
         <x:v>23505</x:v>
       </x:c>
       <x:c r="K32" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A13:H13</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A13:H13</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -4048,7 +4048,7 @@
         <x:v>23514</x:v>
       </x:c>
       <x:c r="K46" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="L46" s="14" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -4086,7 +4086,7 @@
         <x:v>23514</x:v>
       </x:c>
       <x:c r="K47" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="L47" s="15" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -4124,7 +4124,7 @@
         <x:v>23514</x:v>
       </x:c>
       <x:c r="K48" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="L48" s="14" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -4162,7 +4162,7 @@
         <x:v>23514</x:v>
       </x:c>
       <x:c r="K49" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="L49" s="15" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -4200,7 +4200,7 @@
         <x:v>23514</x:v>
       </x:c>
       <x:c r="K50" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="L50" s="14" t="str">
         <x:v>CHECKは単一行。業務Code変換はAPI責任</x:v>
@@ -20503,7 +20503,7 @@
         <x:v>SELECT * FROM public.users WHERE id=900202;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J144" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A8:H8</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A8:H8</x:v>
       </x:c>
       <x:c r="K144" s="14" t="str">
         <x:v>未実施</x:v>
@@ -20541,7 +20541,7 @@
         <x:v>SELECT * FROM public.users WHERE id=900202;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J145" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A9:H9</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A9:H9</x:v>
       </x:c>
       <x:c r="K145" s="15" t="str">
         <x:v>未実施</x:v>
@@ -20579,7 +20579,7 @@
         <x:v>SELECT * FROM public.employees WHERE id=900102;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J146" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A10:H10</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A10:H10</x:v>
       </x:c>
       <x:c r="K146" s="14" t="str">
         <x:v>未実施</x:v>
@@ -20617,7 +20617,7 @@
         <x:v>SELECT * FROM public.employees WHERE id=900102;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J147" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A11:H11</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A11:H11</x:v>
       </x:c>
       <x:c r="K147" s="15" t="str">
         <x:v>未実施</x:v>
@@ -20655,7 +20655,7 @@
         <x:v>SELECT * FROM public.departments WHERE id=900002;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J148" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A12:H12</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A12:H12</x:v>
       </x:c>
       <x:c r="K148" s="14" t="str">
         <x:v>未実施</x:v>
@@ -20693,7 +20693,7 @@
         <x:v>SELECT * FROM public.departments WHERE id=900002;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J149" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A13:H13</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A13:H13</x:v>
       </x:c>
       <x:c r="K149" s="15" t="str">
         <x:v>未実施</x:v>
@@ -20883,7 +20883,7 @@
         <x:v>SELECT * FROM public.departments WHERE id=900002;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J154" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="K154" s="14" t="str">
         <x:v>未実施</x:v>
@@ -20921,7 +20921,7 @@
         <x:v>SELECT * FROM public.employees WHERE id=900102;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J155" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="K155" s="15" t="str">
         <x:v>未実施</x:v>
@@ -20959,7 +20959,7 @@
         <x:v>SELECT * FROM public.users WHERE id=900202;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J156" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="K156" s="14" t="str">
         <x:v>未実施</x:v>
@@ -20997,7 +20997,7 @@
         <x:v>SELECT * FROM public.roles WHERE id=3;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J157" s="15" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="K157" s="15" t="str">
         <x:v>未実施</x:v>
@@ -21035,7 +21035,7 @@
         <x:v>SELECT * FROM public.permissions WHERE id=1;（変更前も同じSELECTを保存。異常時はROLLBACK TO SAVEPOINT後に全列一致を確認）</x:v>
       </x:c>
       <x:c r="J158" s="14" t="str">
-        <x:v>15_DB基本設計書／08_FK・Constraint!A14:H14</x:v>
+        <x:v>15_DB基本設計書／08_論理参照・制約!A14:H14</x:v>
       </x:c>
       <x:c r="K158" s="14" t="str">
         <x:v>未実施</x:v>
